--- a/Data/2024/Lineup/Results.xlsx
+++ b/Data/2024/Lineup/Results.xlsx
@@ -825,6 +825,9 @@
       <c r="O2" s="4">
         <v>10</v>
       </c>
+      <c r="P2" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:25">
       <c r="A3" s="3" t="s">
@@ -872,6 +875,9 @@
       <c r="O3" s="4">
         <v>3</v>
       </c>
+      <c r="P3" s="4">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="5" t="s">
@@ -919,6 +925,9 @@
       <c r="O4" s="4">
         <v>7</v>
       </c>
+      <c r="P4" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="5" t="s">
@@ -966,6 +975,9 @@
       <c r="O5" s="4">
         <v>9</v>
       </c>
+      <c r="P5" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="6" t="s">
@@ -1013,6 +1025,9 @@
       <c r="O6" s="4">
         <v>22</v>
       </c>
+      <c r="P6" s="4">
+        <v>26</v>
+      </c>
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="6" t="s">
@@ -1060,6 +1075,9 @@
       <c r="O7" s="4">
         <v>15</v>
       </c>
+      <c r="P7" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="6" t="s">
@@ -1107,6 +1125,9 @@
       <c r="O8" s="4">
         <v>0</v>
       </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="7" t="s">
@@ -1154,6 +1175,9 @@
       <c r="O9" s="4">
         <v>6</v>
       </c>
+      <c r="P9" s="4">
+        <v>7</v>
+      </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="7" t="s">
@@ -1201,6 +1225,9 @@
       <c r="O10" s="4">
         <v>2</v>
       </c>
+      <c r="P10" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="8" t="s">
@@ -1248,6 +1275,9 @@
       <c r="O11" s="4">
         <v>3</v>
       </c>
+      <c r="P11" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="8" t="s">
@@ -1295,6 +1325,9 @@
       <c r="O12" s="4">
         <v>-18</v>
       </c>
+      <c r="P12" s="4">
+        <v>-2</v>
+      </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="9" t="s">
@@ -1342,6 +1375,9 @@
       <c r="O13" s="4">
         <v>17</v>
       </c>
+      <c r="P13" s="4">
+        <v>56</v>
+      </c>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="9" t="s">
@@ -1389,6 +1425,9 @@
       <c r="O14" s="4">
         <v>30</v>
       </c>
+      <c r="P14" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="10" t="s">
@@ -1436,6 +1475,9 @@
       <c r="O15" s="4">
         <v>46</v>
       </c>
+      <c r="P15" s="4">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="10" t="s">
@@ -1483,6 +1525,9 @@
       <c r="O16" s="4">
         <v>-21</v>
       </c>
+      <c r="P16" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="11" t="s">
@@ -1530,6 +1575,9 @@
       <c r="O17" s="4">
         <v>6</v>
       </c>
+      <c r="P17" s="4">
+        <v>-3</v>
+      </c>
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="11" t="s">
@@ -1577,6 +1625,9 @@
       <c r="O18" s="4">
         <v>8</v>
       </c>
+      <c r="P18" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="12" t="s">
@@ -1624,6 +1675,9 @@
       <c r="O19" s="4">
         <v>35</v>
       </c>
+      <c r="P19" s="4">
+        <v>28</v>
+      </c>
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="12" t="s">
@@ -1671,6 +1725,9 @@
       <c r="O20" s="4">
         <v>19</v>
       </c>
+      <c r="P20" s="4">
+        <v>14</v>
+      </c>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="13" t="s">
@@ -1718,6 +1775,9 @@
       <c r="O21" s="4">
         <v>2</v>
       </c>
+      <c r="P21" s="4">
+        <v>-2</v>
+      </c>
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="13" t="s">
@@ -1765,6 +1825,9 @@
       <c r="O22" s="4">
         <v>2</v>
       </c>
+      <c r="P22" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
@@ -1889,6 +1952,9 @@
       <c r="O25" s="4">
         <v>11</v>
       </c>
+      <c r="P25" s="4">
+        <v>11.5</v>
+      </c>
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="3" t="s">
@@ -1936,6 +2002,9 @@
       <c r="O26" s="4">
         <v>9.699999999999999</v>
       </c>
+      <c r="P26" s="4">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="5" t="s">
@@ -1983,6 +2052,9 @@
       <c r="O27" s="4">
         <v>15.2</v>
       </c>
+      <c r="P27" s="4">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="5" t="s">
@@ -2030,6 +2102,9 @@
       <c r="O28" s="4">
         <v>16.3</v>
       </c>
+      <c r="P28" s="4">
+        <v>16.4</v>
+      </c>
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="6" t="s">
@@ -2077,6 +2152,9 @@
       <c r="O29" s="4">
         <v>23.3</v>
       </c>
+      <c r="P29" s="4">
+        <v>23.6</v>
+      </c>
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="6" t="s">
@@ -2124,6 +2202,9 @@
       <c r="O30" s="4">
         <v>22.5</v>
       </c>
+      <c r="P30" s="4">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="6" t="s">
@@ -2171,6 +2252,9 @@
       <c r="O31" s="4">
         <v>0</v>
       </c>
+      <c r="P31" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="7" t="s">
@@ -2218,6 +2302,9 @@
       <c r="O32" s="4">
         <v>11.3</v>
       </c>
+      <c r="P32" s="4">
+        <v>11.8</v>
+      </c>
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="7" t="s">
@@ -2265,6 +2352,9 @@
       <c r="O33" s="4">
         <v>9.5</v>
       </c>
+      <c r="P33" s="4">
+        <v>9.4</v>
+      </c>
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="8" t="s">
@@ -2312,6 +2402,9 @@
       <c r="O34" s="4">
         <v>7.6</v>
       </c>
+      <c r="P34" s="4">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="8" t="s">
@@ -2359,6 +2452,9 @@
       <c r="O35" s="4">
         <v>7.3</v>
       </c>
+      <c r="P35" s="4">
+        <v>7.1</v>
+      </c>
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="9" t="s">
@@ -2406,6 +2502,9 @@
       <c r="O36" s="4">
         <v>26.2</v>
       </c>
+      <c r="P36" s="4">
+        <v>26.3</v>
+      </c>
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="9" t="s">
@@ -2453,6 +2552,9 @@
       <c r="O37" s="4">
         <v>23.3</v>
       </c>
+      <c r="P37" s="4">
+        <v>23.6</v>
+      </c>
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="10" t="s">
@@ -2500,6 +2602,9 @@
       <c r="O38" s="4">
         <v>23.1</v>
       </c>
+      <c r="P38" s="4">
+        <v>24.1</v>
+      </c>
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="10" t="s">
@@ -2547,6 +2652,9 @@
       <c r="O39" s="4">
         <v>21.2</v>
       </c>
+      <c r="P39" s="4">
+        <v>20.7</v>
+      </c>
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="11" t="s">
@@ -2594,6 +2702,9 @@
       <c r="O40" s="4">
         <v>10.4</v>
       </c>
+      <c r="P40" s="4">
+        <v>10.9</v>
+      </c>
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="11" t="s">
@@ -2641,6 +2752,9 @@
       <c r="O41" s="4">
         <v>10.8</v>
       </c>
+      <c r="P41" s="4">
+        <v>11.3</v>
+      </c>
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="12" t="s">
@@ -2688,6 +2802,9 @@
       <c r="O42" s="4">
         <v>31.1</v>
       </c>
+      <c r="P42" s="4">
+        <v>31.3</v>
+      </c>
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="12" t="s">
@@ -2735,6 +2852,9 @@
       <c r="O43" s="4">
         <v>23</v>
       </c>
+      <c r="P43" s="4">
+        <v>23.3</v>
+      </c>
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="13" t="s">
@@ -2782,6 +2902,9 @@
       <c r="O44" s="4">
         <v>8.9</v>
       </c>
+      <c r="P44" s="4">
+        <v>8.699999999999999</v>
+      </c>
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="13" t="s">
@@ -2829,6 +2952,9 @@
       <c r="O45" s="4">
         <v>5.1</v>
       </c>
+      <c r="P45" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="47" spans="1:25">
       <c r="A47" s="1" t="s">
@@ -2953,8 +3079,11 @@
       <c r="O48" s="4">
         <v>72</v>
       </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="P48" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49" s="3" t="s">
         <v>26</v>
       </c>
@@ -3000,8 +3129,11 @@
       <c r="O49" s="4">
         <v>24</v>
       </c>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="P49" s="4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
       <c r="A50" s="5" t="s">
         <v>27</v>
       </c>
@@ -3047,8 +3179,11 @@
       <c r="O50" s="4">
         <v>88</v>
       </c>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="P50" s="4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
       <c r="A51" s="5" t="s">
         <v>28</v>
       </c>
@@ -3094,8 +3229,11 @@
       <c r="O51" s="4">
         <v>124</v>
       </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="P51" s="4">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52" s="6" t="s">
         <v>29</v>
       </c>
@@ -3141,8 +3279,11 @@
       <c r="O52" s="4">
         <v>326</v>
       </c>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="P52" s="4">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53" s="6" t="s">
         <v>30</v>
       </c>
@@ -3188,8 +3329,11 @@
       <c r="O53" s="4">
         <v>294</v>
       </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="P53" s="4">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54" s="7" t="s">
         <v>32</v>
       </c>
@@ -3235,8 +3379,11 @@
       <c r="O54" s="4">
         <v>87</v>
       </c>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="P54" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55" s="7" t="s">
         <v>33</v>
       </c>
@@ -3282,8 +3429,11 @@
       <c r="O55" s="4">
         <v>76</v>
       </c>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="P55" s="4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56" s="8" t="s">
         <v>34</v>
       </c>
@@ -3329,8 +3479,11 @@
       <c r="O56" s="4">
         <v>36</v>
       </c>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="P56" s="4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
       <c r="A57" s="8" t="s">
         <v>35</v>
       </c>
@@ -3376,8 +3529,11 @@
       <c r="O57" s="4">
         <v>28</v>
       </c>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="P57" s="4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
       <c r="A58" s="9" t="s">
         <v>36</v>
       </c>
@@ -3423,8 +3579,11 @@
       <c r="O58" s="4">
         <v>358</v>
       </c>
-    </row>
-    <row r="59" spans="1:15">
+      <c r="P58" s="4">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
       <c r="A59" s="9" t="s">
         <v>37</v>
       </c>
@@ -3470,8 +3629,11 @@
       <c r="O59" s="4">
         <v>322</v>
       </c>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="P59" s="4">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60" s="10" t="s">
         <v>38</v>
       </c>
@@ -3517,8 +3679,11 @@
       <c r="O60" s="4">
         <v>293</v>
       </c>
-    </row>
-    <row r="61" spans="1:15">
+      <c r="P60" s="4">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
       <c r="A61" s="10" t="s">
         <v>39</v>
       </c>
@@ -3564,8 +3729,11 @@
       <c r="O61" s="4">
         <v>215</v>
       </c>
-    </row>
-    <row r="62" spans="1:15">
+      <c r="P61" s="4">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62" s="11" t="s">
         <v>40</v>
       </c>
@@ -3611,8 +3779,11 @@
       <c r="O62" s="4">
         <v>78</v>
       </c>
-    </row>
-    <row r="63" spans="1:15">
+      <c r="P62" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
       <c r="A63" s="11" t="s">
         <v>41</v>
       </c>
@@ -3658,8 +3829,11 @@
       <c r="O63" s="4">
         <v>40</v>
       </c>
-    </row>
-    <row r="64" spans="1:15">
+      <c r="P63" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
       <c r="A64" s="12" t="s">
         <v>42</v>
       </c>
@@ -3704,6 +3878,9 @@
       </c>
       <c r="O64" s="4">
         <v>445</v>
+      </c>
+      <c r="P64" s="4">
+        <v>473</v>
       </c>
     </row>
     <row r="65" spans="1:25">
@@ -3752,6 +3929,9 @@
       <c r="O65" s="4">
         <v>243</v>
       </c>
+      <c r="P65" s="4">
+        <v>257</v>
+      </c>
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="13" t="s">
@@ -3799,6 +3979,9 @@
       <c r="O66" s="4">
         <v>13</v>
       </c>
+      <c r="P66" s="4">
+        <v>11</v>
+      </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="13" t="s">
@@ -3846,6 +4029,9 @@
       <c r="O67" s="4">
         <v>8</v>
       </c>
+      <c r="P67" s="4">
+        <v>8</v>
+      </c>
     </row>
     <row r="68" spans="1:25">
       <c r="A68" s="6" t="s">
@@ -3893,6 +4079,9 @@
       <c r="O68" s="4">
         <v>26</v>
       </c>
+      <c r="P68" s="4">
+        <v>26</v>
+      </c>
     </row>
     <row r="70" spans="1:25">
       <c r="A70" s="1" t="s">
@@ -4017,6 +4206,9 @@
       <c r="O71" s="4">
         <v>130.8</v>
       </c>
+      <c r="P71" s="4">
+        <v>142.3</v>
+      </c>
     </row>
     <row r="72" spans="1:25">
       <c r="A72" s="3" t="s">
@@ -4064,6 +4256,9 @@
       <c r="O72" s="4">
         <v>118.9</v>
       </c>
+      <c r="P72" s="4">
+        <v>128.5</v>
+      </c>
     </row>
     <row r="73" spans="1:25">
       <c r="A73" s="5" t="s">
@@ -4111,6 +4306,9 @@
       <c r="O73" s="4">
         <v>182.9</v>
       </c>
+      <c r="P73" s="4">
+        <v>198.1</v>
+      </c>
     </row>
     <row r="74" spans="1:25">
       <c r="A74" s="5" t="s">
@@ -4158,6 +4356,9 @@
       <c r="O74" s="4">
         <v>228.9</v>
       </c>
+      <c r="P74" s="4">
+        <v>245.3</v>
+      </c>
     </row>
     <row r="75" spans="1:25">
       <c r="A75" s="6" t="s">
@@ -4205,6 +4406,9 @@
       <c r="O75" s="4">
         <v>308.4</v>
       </c>
+      <c r="P75" s="4">
+        <v>332</v>
+      </c>
     </row>
     <row r="76" spans="1:25">
       <c r="A76" s="6" t="s">
@@ -4252,6 +4456,9 @@
       <c r="O76" s="4">
         <v>271.6</v>
       </c>
+      <c r="P76" s="4">
+        <v>294.2</v>
+      </c>
     </row>
     <row r="77" spans="1:25">
       <c r="A77" s="7" t="s">
@@ -4299,6 +4506,9 @@
       <c r="O77" s="4">
         <v>124.1</v>
       </c>
+      <c r="P77" s="4">
+        <v>135.9</v>
+      </c>
     </row>
     <row r="78" spans="1:25">
       <c r="A78" s="7" t="s">
@@ -4346,6 +4556,9 @@
       <c r="O78" s="4">
         <v>111.5</v>
       </c>
+      <c r="P78" s="4">
+        <v>120.9</v>
+      </c>
     </row>
     <row r="79" spans="1:25">
       <c r="A79" s="8" t="s">
@@ -4393,6 +4606,9 @@
       <c r="O79" s="4">
         <v>96.80000000000001</v>
       </c>
+      <c r="P79" s="4">
+        <v>104.3</v>
+      </c>
     </row>
     <row r="80" spans="1:25">
       <c r="A80" s="8" t="s">
@@ -4440,6 +4656,9 @@
       <c r="O80" s="4">
         <v>101.8</v>
       </c>
+      <c r="P80" s="4">
+        <v>108.9</v>
+      </c>
     </row>
     <row r="81" spans="1:25">
       <c r="A81" s="9" t="s">
@@ -4487,6 +4706,9 @@
       <c r="O81" s="4">
         <v>346.2</v>
       </c>
+      <c r="P81" s="4">
+        <v>372.5</v>
+      </c>
     </row>
     <row r="82" spans="1:25">
       <c r="A82" s="9" t="s">
@@ -4534,6 +4756,9 @@
       <c r="O82" s="4">
         <v>289.7</v>
       </c>
+      <c r="P82" s="4">
+        <v>313.3000000000001</v>
+      </c>
     </row>
     <row r="83" spans="1:25">
       <c r="A83" s="10" t="s">
@@ -4581,6 +4806,9 @@
       <c r="O83" s="4">
         <v>283.6</v>
       </c>
+      <c r="P83" s="4">
+        <v>307.7</v>
+      </c>
     </row>
     <row r="84" spans="1:25">
       <c r="A84" s="10" t="s">
@@ -4628,6 +4856,9 @@
       <c r="O84" s="4">
         <v>278.3</v>
       </c>
+      <c r="P84" s="4">
+        <v>299</v>
+      </c>
     </row>
     <row r="85" spans="1:25">
       <c r="A85" s="11" t="s">
@@ -4675,6 +4906,9 @@
       <c r="O85" s="4">
         <v>127</v>
       </c>
+      <c r="P85" s="4">
+        <v>137.9</v>
+      </c>
     </row>
     <row r="86" spans="1:25">
       <c r="A86" s="11" t="s">
@@ -4722,6 +4956,9 @@
       <c r="O86" s="4">
         <v>132.5</v>
       </c>
+      <c r="P86" s="4">
+        <v>143.8</v>
+      </c>
     </row>
     <row r="87" spans="1:25">
       <c r="A87" s="12" t="s">
@@ -4769,6 +5006,9 @@
       <c r="O87" s="4">
         <v>425.9</v>
       </c>
+      <c r="P87" s="4">
+        <v>457.2</v>
+      </c>
     </row>
     <row r="88" spans="1:25">
       <c r="A88" s="12" t="s">
@@ -4816,6 +5056,9 @@
       <c r="O88" s="4">
         <v>315.1</v>
       </c>
+      <c r="P88" s="4">
+        <v>338.4</v>
+      </c>
     </row>
     <row r="89" spans="1:25">
       <c r="A89" s="13" t="s">
@@ -4863,6 +5106,9 @@
       <c r="O89" s="4">
         <v>109.6</v>
       </c>
+      <c r="P89" s="4">
+        <v>118.3</v>
+      </c>
     </row>
     <row r="90" spans="1:25">
       <c r="A90" s="13" t="s">
@@ -4910,6 +5156,9 @@
       <c r="O90" s="4">
         <v>79.5</v>
       </c>
+      <c r="P90" s="4">
+        <v>84.5</v>
+      </c>
     </row>
     <row r="91" spans="1:25">
       <c r="A91" s="6" t="s">
@@ -4957,6 +5206,9 @@
       <c r="O91" s="4">
         <v>14</v>
       </c>
+      <c r="P91" s="4">
+        <v>14</v>
+      </c>
     </row>
     <row r="93" spans="1:25">
       <c r="A93" s="1" t="s">
@@ -5081,6 +5333,9 @@
       <c r="O94" s="4">
         <v>5.142857142857143</v>
       </c>
+      <c r="P94" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="95" spans="1:25">
       <c r="A95" s="3" t="s">
@@ -5128,6 +5383,9 @@
       <c r="O95" s="4">
         <v>1.714285714285714</v>
       </c>
+      <c r="P95" s="4">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="96" spans="1:25">
       <c r="A96" s="5" t="s">
@@ -5175,8 +5433,11 @@
       <c r="O96" s="4">
         <v>6.285714285714286</v>
       </c>
-    </row>
-    <row r="97" spans="1:15">
+      <c r="P96" s="4">
+        <v>5.933333333333334</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
       <c r="A97" s="5" t="s">
         <v>28</v>
       </c>
@@ -5222,8 +5483,11 @@
       <c r="O97" s="4">
         <v>8.857142857142858</v>
       </c>
-    </row>
-    <row r="98" spans="1:15">
+      <c r="P97" s="4">
+        <v>8.666666666666666</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
       <c r="A98" s="6" t="s">
         <v>29</v>
       </c>
@@ -5269,8 +5533,11 @@
       <c r="O98" s="4">
         <v>23.28571428571428</v>
       </c>
-    </row>
-    <row r="99" spans="1:15">
+      <c r="P98" s="4">
+        <v>23.46666666666667</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
       <c r="A99" s="6" t="s">
         <v>30</v>
       </c>
@@ -5316,8 +5583,11 @@
       <c r="O99" s="4">
         <v>21</v>
       </c>
-    </row>
-    <row r="100" spans="1:15">
+      <c r="P99" s="4">
+        <v>20.93333333333333</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
       <c r="A100" s="7" t="s">
         <v>32</v>
       </c>
@@ -5363,8 +5633,11 @@
       <c r="O100" s="4">
         <v>6.214285714285714</v>
       </c>
-    </row>
-    <row r="101" spans="1:15">
+      <c r="P100" s="4">
+        <v>6.266666666666667</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
       <c r="A101" s="7" t="s">
         <v>33</v>
       </c>
@@ -5410,8 +5683,11 @@
       <c r="O101" s="4">
         <v>5.428571428571429</v>
       </c>
-    </row>
-    <row r="102" spans="1:15">
+      <c r="P101" s="4">
+        <v>5.466666666666667</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
       <c r="A102" s="8" t="s">
         <v>34</v>
       </c>
@@ -5457,8 +5733,11 @@
       <c r="O102" s="4">
         <v>2.571428571428572</v>
       </c>
-    </row>
-    <row r="103" spans="1:15">
+      <c r="P102" s="4">
+        <v>2.466666666666667</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
       <c r="A103" s="8" t="s">
         <v>35</v>
       </c>
@@ -5504,8 +5783,11 @@
       <c r="O103" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" spans="1:15">
+      <c r="P103" s="4">
+        <v>1.733333333333333</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
       <c r="A104" s="9" t="s">
         <v>36</v>
       </c>
@@ -5551,8 +5833,11 @@
       <c r="O104" s="4">
         <v>25.57142857142857</v>
       </c>
-    </row>
-    <row r="105" spans="1:15">
+      <c r="P104" s="4">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
       <c r="A105" s="9" t="s">
         <v>37</v>
       </c>
@@ -5598,8 +5883,11 @@
       <c r="O105" s="4">
         <v>23</v>
       </c>
-    </row>
-    <row r="106" spans="1:15">
+      <c r="P105" s="4">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
       <c r="A106" s="10" t="s">
         <v>38</v>
       </c>
@@ -5645,8 +5933,11 @@
       <c r="O106" s="4">
         <v>20.92857142857143</v>
       </c>
-    </row>
-    <row r="107" spans="1:15">
+      <c r="P106" s="4">
+        <v>20.93333333333333</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16">
       <c r="A107" s="10" t="s">
         <v>39</v>
       </c>
@@ -5692,8 +5983,11 @@
       <c r="O107" s="4">
         <v>15.35714285714286</v>
       </c>
-    </row>
-    <row r="108" spans="1:15">
+      <c r="P107" s="4">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
       <c r="A108" s="11" t="s">
         <v>40</v>
       </c>
@@ -5739,8 +6033,11 @@
       <c r="O108" s="4">
         <v>5.571428571428571</v>
       </c>
-    </row>
-    <row r="109" spans="1:15">
+      <c r="P108" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
       <c r="A109" s="11" t="s">
         <v>41</v>
       </c>
@@ -5786,8 +6083,11 @@
       <c r="O109" s="4">
         <v>2.857142857142857</v>
       </c>
-    </row>
-    <row r="110" spans="1:15">
+      <c r="P109" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
       <c r="A110" s="12" t="s">
         <v>42</v>
       </c>
@@ -5833,8 +6133,11 @@
       <c r="O110" s="4">
         <v>31.78571428571428</v>
       </c>
-    </row>
-    <row r="111" spans="1:15">
+      <c r="P110" s="4">
+        <v>31.53333333333333</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
       <c r="A111" s="12" t="s">
         <v>43</v>
       </c>
@@ -5880,8 +6183,11 @@
       <c r="O111" s="4">
         <v>17.35714285714286</v>
       </c>
-    </row>
-    <row r="112" spans="1:15">
+      <c r="P111" s="4">
+        <v>17.13333333333333</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
       <c r="A112" s="13" t="s">
         <v>44</v>
       </c>
@@ -5926,6 +6232,9 @@
       </c>
       <c r="O112" s="4">
         <v>0.9285714285714286</v>
+      </c>
+      <c r="P112" s="4">
+        <v>0.7333333333333333</v>
       </c>
     </row>
     <row r="113" spans="1:25">
@@ -5974,6 +6283,9 @@
       <c r="O113" s="4">
         <v>0.5714285714285714</v>
       </c>
+      <c r="P113" s="4">
+        <v>0.5333333333333333</v>
+      </c>
     </row>
     <row r="114" spans="1:25">
       <c r="A114" s="6" t="s">
@@ -6021,6 +6333,9 @@
       <c r="O114" s="4">
         <v>1.857142857142857</v>
       </c>
+      <c r="P114" s="4">
+        <v>1.733333333333333</v>
+      </c>
     </row>
     <row r="116" spans="1:25">
       <c r="A116" s="1" t="s">
@@ -6145,6 +6460,9 @@
       <c r="O117" s="4">
         <v>9.342857142857143</v>
       </c>
+      <c r="P117" s="4">
+        <v>9.486666666666668</v>
+      </c>
     </row>
     <row r="118" spans="1:25">
       <c r="A118" s="3" t="s">
@@ -6192,6 +6510,9 @@
       <c r="O118" s="4">
         <v>8.492857142857142</v>
       </c>
+      <c r="P118" s="4">
+        <v>8.566666666666666</v>
+      </c>
     </row>
     <row r="119" spans="1:25">
       <c r="A119" s="5" t="s">
@@ -6239,6 +6560,9 @@
       <c r="O119" s="4">
         <v>13.06428571428571</v>
       </c>
+      <c r="P119" s="4">
+        <v>13.20666666666667</v>
+      </c>
     </row>
     <row r="120" spans="1:25">
       <c r="A120" s="5" t="s">
@@ -6286,6 +6610,9 @@
       <c r="O120" s="4">
         <v>16.35</v>
       </c>
+      <c r="P120" s="4">
+        <v>16.35333333333334</v>
+      </c>
     </row>
     <row r="121" spans="1:25">
       <c r="A121" s="6" t="s">
@@ -6333,6 +6660,9 @@
       <c r="O121" s="4">
         <v>22.02857142857143</v>
       </c>
+      <c r="P121" s="4">
+        <v>22.13333333333333</v>
+      </c>
     </row>
     <row r="122" spans="1:25">
       <c r="A122" s="6" t="s">
@@ -6380,6 +6710,9 @@
       <c r="O122" s="4">
         <v>19.4</v>
       </c>
+      <c r="P122" s="4">
+        <v>19.61333333333334</v>
+      </c>
     </row>
     <row r="123" spans="1:25">
       <c r="A123" s="7" t="s">
@@ -6427,6 +6760,9 @@
       <c r="O123" s="4">
         <v>8.864285714285716</v>
       </c>
+      <c r="P123" s="4">
+        <v>9.06</v>
+      </c>
     </row>
     <row r="124" spans="1:25">
       <c r="A124" s="7" t="s">
@@ -6474,6 +6810,9 @@
       <c r="O124" s="4">
         <v>7.964285714285715</v>
       </c>
+      <c r="P124" s="4">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="125" spans="1:25">
       <c r="A125" s="8" t="s">
@@ -6521,6 +6860,9 @@
       <c r="O125" s="4">
         <v>6.914285714285715</v>
       </c>
+      <c r="P125" s="4">
+        <v>6.953333333333334</v>
+      </c>
     </row>
     <row r="126" spans="1:25">
       <c r="A126" s="8" t="s">
@@ -6568,6 +6910,9 @@
       <c r="O126" s="4">
         <v>7.271428571428571</v>
       </c>
+      <c r="P126" s="4">
+        <v>7.26</v>
+      </c>
     </row>
     <row r="127" spans="1:25">
       <c r="A127" s="9" t="s">
@@ -6615,6 +6960,9 @@
       <c r="O127" s="4">
         <v>24.72857142857143</v>
       </c>
+      <c r="P127" s="4">
+        <v>24.83333333333333</v>
+      </c>
     </row>
     <row r="128" spans="1:25">
       <c r="A128" s="9" t="s">
@@ -6662,6 +7010,9 @@
       <c r="O128" s="4">
         <v>20.69285714285715</v>
       </c>
+      <c r="P128" s="4">
+        <v>20.88666666666667</v>
+      </c>
     </row>
     <row r="129" spans="1:25">
       <c r="A129" s="10" t="s">
@@ -6709,6 +7060,9 @@
       <c r="O129" s="4">
         <v>20.25714285714286</v>
       </c>
+      <c r="P129" s="4">
+        <v>20.51333333333334</v>
+      </c>
     </row>
     <row r="130" spans="1:25">
       <c r="A130" s="10" t="s">
@@ -6756,6 +7110,9 @@
       <c r="O130" s="4">
         <v>19.87857142857143</v>
       </c>
+      <c r="P130" s="4">
+        <v>19.93333333333333</v>
+      </c>
     </row>
     <row r="131" spans="1:25">
       <c r="A131" s="11" t="s">
@@ -6803,6 +7160,9 @@
       <c r="O131" s="4">
         <v>9.071428571428571</v>
       </c>
+      <c r="P131" s="4">
+        <v>9.193333333333333</v>
+      </c>
     </row>
     <row r="132" spans="1:25">
       <c r="A132" s="11" t="s">
@@ -6850,6 +7210,9 @@
       <c r="O132" s="4">
         <v>9.464285714285714</v>
       </c>
+      <c r="P132" s="4">
+        <v>9.586666666666668</v>
+      </c>
     </row>
     <row r="133" spans="1:25">
       <c r="A133" s="12" t="s">
@@ -6897,6 +7260,9 @@
       <c r="O133" s="4">
         <v>30.42142857142857</v>
       </c>
+      <c r="P133" s="4">
+        <v>30.48</v>
+      </c>
     </row>
     <row r="134" spans="1:25">
       <c r="A134" s="12" t="s">
@@ -6944,6 +7310,9 @@
       <c r="O134" s="4">
         <v>22.50714285714286</v>
       </c>
+      <c r="P134" s="4">
+        <v>22.56</v>
+      </c>
     </row>
     <row r="135" spans="1:25">
       <c r="A135" s="13" t="s">
@@ -6991,6 +7360,9 @@
       <c r="O135" s="4">
         <v>7.828571428571428</v>
       </c>
+      <c r="P135" s="4">
+        <v>7.886666666666667</v>
+      </c>
     </row>
     <row r="136" spans="1:25">
       <c r="A136" s="13" t="s">
@@ -7038,6 +7410,9 @@
       <c r="O136" s="4">
         <v>5.678571428571429</v>
       </c>
+      <c r="P136" s="4">
+        <v>5.633333333333334</v>
+      </c>
     </row>
     <row r="137" spans="1:25">
       <c r="A137" s="6" t="s">
@@ -7085,6 +7460,9 @@
       <c r="O137" s="4">
         <v>1</v>
       </c>
+      <c r="P137" s="4">
+        <v>0.9333333333333333</v>
+      </c>
     </row>
     <row r="139" spans="1:25">
       <c r="A139" s="1" t="s">
@@ -7209,6 +7587,9 @@
       <c r="O140" s="4">
         <v>0.9090909090909091</v>
       </c>
+      <c r="P140" s="4">
+        <v>0.2608695652173913</v>
+      </c>
     </row>
     <row r="141" spans="1:25">
       <c r="A141" s="3" t="s">
@@ -7256,6 +7637,9 @@
       <c r="O141" s="4">
         <v>0.3092783505154639</v>
       </c>
+      <c r="P141" s="4">
+        <v>0.9375</v>
+      </c>
     </row>
     <row r="142" spans="1:25">
       <c r="A142" s="5" t="s">
@@ -7303,6 +7687,9 @@
       <c r="O142" s="4">
         <v>0.4605263157894737</v>
       </c>
+      <c r="P142" s="4">
+        <v>0.06578947368421052</v>
+      </c>
     </row>
     <row r="143" spans="1:25">
       <c r="A143" s="5" t="s">
@@ -7350,6 +7737,9 @@
       <c r="O143" s="4">
         <v>0.5521472392638036</v>
       </c>
+      <c r="P143" s="4">
+        <v>0.3658536585365854</v>
+      </c>
     </row>
     <row r="144" spans="1:25">
       <c r="A144" s="6" t="s">
@@ -7397,8 +7787,11 @@
       <c r="O144" s="4">
         <v>0.944206008583691</v>
       </c>
-    </row>
-    <row r="145" spans="1:15">
+      <c r="P144" s="4">
+        <v>1.101694915254237</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
       <c r="A145" s="6" t="s">
         <v>30</v>
       </c>
@@ -7444,8 +7837,11 @@
       <c r="O145" s="4">
         <v>0.6666666666666666</v>
       </c>
-    </row>
-    <row r="146" spans="1:15">
+      <c r="P145" s="4">
+        <v>0.8849557522123893</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
       <c r="A146" s="7" t="s">
         <v>32</v>
       </c>
@@ -7491,8 +7887,11 @@
       <c r="O146" s="4">
         <v>0.5309734513274336</v>
       </c>
-    </row>
-    <row r="147" spans="1:15">
+      <c r="P146" s="4">
+        <v>0.5932203389830508</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
       <c r="A147" s="7" t="s">
         <v>33</v>
       </c>
@@ -7538,8 +7937,11 @@
       <c r="O147" s="4">
         <v>0.2105263157894737</v>
       </c>
-    </row>
-    <row r="148" spans="1:15">
+      <c r="P147" s="4">
+        <v>0.6382978723404255</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
       <c r="A148" s="8" t="s">
         <v>34</v>
       </c>
@@ -7585,8 +7987,11 @@
       <c r="O148" s="4">
         <v>0.3947368421052632</v>
       </c>
-    </row>
-    <row r="149" spans="1:15">
+      <c r="P148" s="4">
+        <v>0.1333333333333333</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16">
       <c r="A149" s="8" t="s">
         <v>35</v>
       </c>
@@ -7632,8 +8037,11 @@
       <c r="O149" s="4">
         <v>-2.465753424657534</v>
       </c>
-    </row>
-    <row r="150" spans="1:15">
+      <c r="P149" s="4">
+        <v>-0.2816901408450704</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16">
       <c r="A150" s="9" t="s">
         <v>36</v>
       </c>
@@ -7679,8 +8087,11 @@
       <c r="O150" s="4">
         <v>0.648854961832061</v>
       </c>
-    </row>
-    <row r="151" spans="1:15">
+      <c r="P150" s="4">
+        <v>2.129277566539924</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16">
       <c r="A151" s="9" t="s">
         <v>37</v>
       </c>
@@ -7726,8 +8137,11 @@
       <c r="O151" s="4">
         <v>1.28755364806867</v>
       </c>
-    </row>
-    <row r="152" spans="1:15">
+      <c r="P151" s="4">
+        <v>0.847457627118644</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16">
       <c r="A152" s="10" t="s">
         <v>38</v>
       </c>
@@ -7773,8 +8187,11 @@
       <c r="O152" s="4">
         <v>1.991341991341991</v>
       </c>
-    </row>
-    <row r="153" spans="1:15">
+      <c r="P152" s="4">
+        <v>0.871369294605809</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16">
       <c r="A153" s="10" t="s">
         <v>39</v>
       </c>
@@ -7820,8 +8237,11 @@
       <c r="O153" s="4">
         <v>-0.9905660377358491</v>
       </c>
-    </row>
-    <row r="154" spans="1:15">
+      <c r="P153" s="4">
+        <v>0.6280193236714976</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16">
       <c r="A154" s="11" t="s">
         <v>40</v>
       </c>
@@ -7867,8 +8287,11 @@
       <c r="O154" s="4">
         <v>0.5769230769230769</v>
       </c>
-    </row>
-    <row r="155" spans="1:15">
+      <c r="P154" s="4">
+        <v>-0.2752293577981652</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16">
       <c r="A155" s="11" t="s">
         <v>41</v>
       </c>
@@ -7914,8 +8337,11 @@
       <c r="O155" s="4">
         <v>0.7407407407407407</v>
       </c>
-    </row>
-    <row r="156" spans="1:15">
+      <c r="P155" s="4">
+        <v>0.4424778761061947</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16">
       <c r="A156" s="12" t="s">
         <v>42</v>
       </c>
@@ -7961,8 +8387,11 @@
       <c r="O156" s="4">
         <v>1.12540192926045</v>
       </c>
-    </row>
-    <row r="157" spans="1:15">
+      <c r="P156" s="4">
+        <v>0.8945686900958466</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16">
       <c r="A157" s="12" t="s">
         <v>43</v>
       </c>
@@ -8008,8 +8437,11 @@
       <c r="O157" s="4">
         <v>0.8260869565217391</v>
       </c>
-    </row>
-    <row r="158" spans="1:15">
+      <c r="P157" s="4">
+        <v>0.6008583690987124</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16">
       <c r="A158" s="13" t="s">
         <v>44</v>
       </c>
@@ -8055,8 +8487,11 @@
       <c r="O158" s="4">
         <v>0.2247191011235955</v>
       </c>
-    </row>
-    <row r="159" spans="1:15">
+      <c r="P158" s="4">
+        <v>-0.2298850574712644</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16">
       <c r="A159" s="13" t="s">
         <v>45</v>
       </c>
@@ -8102,8 +8537,11 @@
       <c r="O159" s="4">
         <v>0.3921568627450981</v>
       </c>
-    </row>
-    <row r="160" spans="1:15">
+      <c r="P159" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16">
       <c r="A160" s="6" t="s">
         <v>31</v>
       </c>
@@ -8147,6 +8585,9 @@
         <v>0</v>
       </c>
       <c r="O160" s="4">
+        <v>0</v>
+      </c>
+      <c r="P160" s="4">
         <v>0</v>
       </c>
     </row>
@@ -8273,6 +8714,9 @@
       <c r="O163" s="4">
         <v>0.5901639344262295</v>
       </c>
+      <c r="P163" s="4">
+        <v>0.5617977528089888</v>
+      </c>
     </row>
     <row r="164" spans="1:25">
       <c r="A164" s="3" t="s">
@@ -8320,6 +8764,9 @@
       <c r="O164" s="4">
         <v>0.2018502943650126</v>
       </c>
+      <c r="P164" s="4">
+        <v>0.2568093385214008</v>
+      </c>
     </row>
     <row r="165" spans="1:25">
       <c r="A165" s="5" t="s">
@@ -8367,6 +8814,9 @@
       <c r="O165" s="4">
         <v>0.4811372334609076</v>
       </c>
+      <c r="P165" s="4">
+        <v>0.4492680464411913</v>
+      </c>
     </row>
     <row r="166" spans="1:25">
       <c r="A166" s="5" t="s">
@@ -8414,6 +8864,9 @@
       <c r="O166" s="4">
         <v>0.5417212756662297</v>
       </c>
+      <c r="P166" s="4">
+        <v>0.5299633102323685</v>
+      </c>
     </row>
     <row r="167" spans="1:25">
       <c r="A167" s="6" t="s">
@@ -8461,6 +8914,9 @@
       <c r="O167" s="4">
         <v>1.057068741893645</v>
       </c>
+      <c r="P167" s="4">
+        <v>1.060240963855422</v>
+      </c>
     </row>
     <row r="168" spans="1:25">
       <c r="A168" s="6" t="s">
@@ -8508,6 +8964,9 @@
       <c r="O168" s="4">
         <v>1.082474226804124</v>
       </c>
+      <c r="P168" s="4">
+        <v>1.067301155676411</v>
+      </c>
     </row>
     <row r="169" spans="1:25">
       <c r="A169" s="7" t="s">
@@ -8555,6 +9014,9 @@
       <c r="O169" s="4">
         <v>0.7010475423045931</v>
       </c>
+      <c r="P169" s="4">
+        <v>0.6916850625459897</v>
+      </c>
     </row>
     <row r="170" spans="1:25">
       <c r="A170" s="7" t="s">
@@ -8602,6 +9064,9 @@
       <c r="O170" s="4">
         <v>0.7465618860510805</v>
       </c>
+      <c r="P170" s="4">
+        <v>0.737410071942446</v>
+      </c>
     </row>
     <row r="171" spans="1:25">
       <c r="A171" s="8" t="s">
@@ -8649,6 +9114,9 @@
       <c r="O171" s="4">
         <v>0.3982300884955752</v>
       </c>
+      <c r="P171" s="4">
+        <v>0.3779366700715015</v>
+      </c>
     </row>
     <row r="172" spans="1:25">
       <c r="A172" s="8" t="s">
@@ -8696,6 +9164,9 @@
       <c r="O172" s="4">
         <v>0.2969247083775186</v>
       </c>
+      <c r="P172" s="4">
+        <v>0.2564102564102564</v>
+      </c>
     </row>
     <row r="173" spans="1:25">
       <c r="A173" s="9" t="s">
@@ -8743,6 +9214,9 @@
       <c r="O173" s="4">
         <v>1.034084344309648</v>
       </c>
+      <c r="P173" s="4">
+        <v>1.111409395973154</v>
+      </c>
     </row>
     <row r="174" spans="1:25">
       <c r="A174" s="9" t="s">
@@ -8790,6 +9264,9 @@
       <c r="O174" s="4">
         <v>1.111494649637556</v>
       </c>
+      <c r="P174" s="4">
+        <v>1.091605489945739</v>
+      </c>
     </row>
     <row r="175" spans="1:25">
       <c r="A175" s="10" t="s">
@@ -8837,6 +9314,9 @@
       <c r="O175" s="4">
         <v>1.033145275035261</v>
       </c>
+      <c r="P175" s="4">
+        <v>1.020474488137797</v>
+      </c>
     </row>
     <row r="176" spans="1:25">
       <c r="A176" s="10" t="s">
@@ -8884,8 +9364,11 @@
       <c r="O176" s="4">
         <v>0.7725476104922745</v>
       </c>
-    </row>
-    <row r="177" spans="1:15">
+      <c r="P176" s="4">
+        <v>0.7625418060200669</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16">
       <c r="A177" s="11" t="s">
         <v>40</v>
       </c>
@@ -8931,8 +9414,11 @@
       <c r="O177" s="4">
         <v>0.6655290102389079</v>
       </c>
-    </row>
-    <row r="178" spans="1:15">
+      <c r="P177" s="4">
+        <v>0.585480093676815</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16">
       <c r="A178" s="11" t="s">
         <v>41</v>
       </c>
@@ -8978,8 +9464,11 @@
       <c r="O178" s="4">
         <v>0.3493449781659388</v>
       </c>
-    </row>
-    <row r="179" spans="1:15">
+      <c r="P178" s="4">
+        <v>0.3577106518282989</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16">
       <c r="A179" s="12" t="s">
         <v>42</v>
       </c>
@@ -9025,8 +9514,11 @@
       <c r="O179" s="4">
         <v>1.044846208030054</v>
       </c>
-    </row>
-    <row r="180" spans="1:15">
+      <c r="P179" s="4">
+        <v>1.034558180227472</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16">
       <c r="A180" s="12" t="s">
         <v>43</v>
       </c>
@@ -9072,8 +9564,11 @@
       <c r="O180" s="4">
         <v>0.7711837511900983</v>
       </c>
-    </row>
-    <row r="181" spans="1:15">
+      <c r="P180" s="4">
+        <v>0.7594562647754137</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16">
       <c r="A181" s="13" t="s">
         <v>44</v>
       </c>
@@ -9119,8 +9614,11 @@
       <c r="O181" s="4">
         <v>0.1267056530214425</v>
       </c>
-    </row>
-    <row r="182" spans="1:15">
+      <c r="P181" s="4">
+        <v>0.09883198562443846</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16">
       <c r="A182" s="13" t="s">
         <v>45</v>
       </c>
@@ -9166,8 +9664,11 @@
       <c r="O182" s="4">
         <v>0.1174743024963289</v>
       </c>
-    </row>
-    <row r="183" spans="1:15">
+      <c r="P182" s="4">
+        <v>0.1174743024963289</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16">
       <c r="A183" s="6" t="s">
         <v>31</v>
       </c>
@@ -9211,6 +9712,9 @@
         <v>1.857142857142857</v>
       </c>
       <c r="O183" s="4">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="P183" s="4">
         <v>1.857142857142857</v>
       </c>
     </row>
@@ -9342,10 +9846,13 @@
         <v>-12</v>
       </c>
       <c r="N2" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="O2" s="4">
         <v>18</v>
+      </c>
+      <c r="P2" s="4">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -9394,6 +9901,9 @@
       <c r="O3" s="4">
         <v>21</v>
       </c>
+      <c r="P3" s="4">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="6" t="s">
@@ -9441,6 +9951,9 @@
       <c r="O4" s="4">
         <v>47</v>
       </c>
+      <c r="P4" s="4">
+        <v>59</v>
+      </c>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="7" t="s">
@@ -9488,6 +10001,9 @@
       <c r="O5" s="4">
         <v>7</v>
       </c>
+      <c r="P5" s="4">
+        <v>16</v>
+      </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="8" t="s">
@@ -9535,6 +10051,9 @@
       <c r="O6" s="4">
         <v>-14</v>
       </c>
+      <c r="P6" s="4">
+        <v>-2</v>
+      </c>
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="9" t="s">
@@ -9582,6 +10101,9 @@
       <c r="O7" s="4">
         <v>67</v>
       </c>
+      <c r="P7" s="4">
+        <v>81</v>
+      </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="10" t="s">
@@ -9629,6 +10151,9 @@
       <c r="O8" s="4">
         <v>25</v>
       </c>
+      <c r="P8" s="4">
+        <v>39</v>
+      </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="11" t="s">
@@ -9674,7 +10199,10 @@
         <v>25</v>
       </c>
       <c r="O9" s="4">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="P9" s="4">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -9718,10 +10246,13 @@
         <v>55</v>
       </c>
       <c r="N10" s="4">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O10" s="4">
         <v>69</v>
+      </c>
+      <c r="P10" s="4">
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -9770,6 +10301,9 @@
       <c r="O11" s="4">
         <v>5</v>
       </c>
+      <c r="P11" s="4">
+        <v>-2</v>
+      </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
@@ -9894,6 +10428,9 @@
       <c r="O14" s="4">
         <v>9.699999999999999</v>
       </c>
+      <c r="P14" s="4">
+        <v>10.2</v>
+      </c>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="5" t="s">
@@ -9941,6 +10478,9 @@
       <c r="O15" s="4">
         <v>15.5</v>
       </c>
+      <c r="P15" s="4">
+        <v>15.6</v>
+      </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="6" t="s">
@@ -9988,6 +10528,9 @@
       <c r="O16" s="4">
         <v>23.4</v>
       </c>
+      <c r="P16" s="4">
+        <v>23.7</v>
+      </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="7" t="s">
@@ -10035,6 +10578,9 @@
       <c r="O17" s="4">
         <v>10.3</v>
       </c>
+      <c r="P17" s="4">
+        <v>10.2</v>
+      </c>
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="8" t="s">
@@ -10082,6 +10628,9 @@
       <c r="O18" s="4">
         <v>6.9</v>
       </c>
+      <c r="P18" s="4">
+        <v>6.7</v>
+      </c>
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="9" t="s">
@@ -10129,6 +10678,9 @@
       <c r="O19" s="4">
         <v>25.9</v>
       </c>
+      <c r="P19" s="4">
+        <v>26</v>
+      </c>
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="10" t="s">
@@ -10176,6 +10728,9 @@
       <c r="O20" s="4">
         <v>22.9</v>
       </c>
+      <c r="P20" s="4">
+        <v>23</v>
+      </c>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="11" t="s">
@@ -10223,6 +10778,9 @@
       <c r="O21" s="4">
         <v>11.2</v>
       </c>
+      <c r="P21" s="4">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="12" t="s">
@@ -10270,6 +10828,9 @@
       <c r="O22" s="4">
         <v>29</v>
       </c>
+      <c r="P22" s="4">
+        <v>29.1</v>
+      </c>
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="13" t="s">
@@ -10317,6 +10878,9 @@
       <c r="O23" s="4">
         <v>6.5</v>
       </c>
+      <c r="P23" s="4">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
@@ -10436,10 +11000,13 @@
         <v>130</v>
       </c>
       <c r="N26" s="4">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O26" s="4">
-        <v>143</v>
+        <v>138</v>
+      </c>
+      <c r="P26" s="4">
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -10488,6 +11055,9 @@
       <c r="O27" s="4">
         <v>296</v>
       </c>
+      <c r="P27" s="4">
+        <v>313</v>
+      </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="6" t="s">
@@ -10535,6 +11105,9 @@
       <c r="O28" s="4">
         <v>780</v>
       </c>
+      <c r="P28" s="4">
+        <v>839</v>
+      </c>
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="7" t="s">
@@ -10582,6 +11155,9 @@
       <c r="O29" s="4">
         <v>202</v>
       </c>
+      <c r="P29" s="4">
+        <v>218</v>
+      </c>
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="8" t="s">
@@ -10629,6 +11205,9 @@
       <c r="O30" s="4">
         <v>73</v>
       </c>
+      <c r="P30" s="4">
+        <v>71</v>
+      </c>
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="9" t="s">
@@ -10676,6 +11255,9 @@
       <c r="O31" s="4">
         <v>766</v>
       </c>
+      <c r="P31" s="4">
+        <v>847</v>
+      </c>
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="10" t="s">
@@ -10723,6 +11305,9 @@
       <c r="O32" s="4">
         <v>628</v>
       </c>
+      <c r="P32" s="4">
+        <v>667</v>
+      </c>
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="11" t="s">
@@ -10768,7 +11353,10 @@
         <v>178</v>
       </c>
       <c r="O33" s="4">
-        <v>195</v>
+        <v>196</v>
+      </c>
+      <c r="P33" s="4">
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -10812,10 +11400,13 @@
         <v>817</v>
       </c>
       <c r="N34" s="4">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="O34" s="4">
-        <v>928</v>
+        <v>933</v>
+      </c>
+      <c r="P34" s="4">
+        <v>985</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -10864,6 +11455,9 @@
       <c r="O35" s="4">
         <v>45</v>
       </c>
+      <c r="P35" s="4">
+        <v>43</v>
+      </c>
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
@@ -10988,6 +11582,9 @@
       <c r="O38" s="4">
         <v>121.8</v>
       </c>
+      <c r="P38" s="4">
+        <v>132</v>
+      </c>
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="5" t="s">
@@ -11035,6 +11632,9 @@
       <c r="O39" s="4">
         <v>208.1</v>
       </c>
+      <c r="P39" s="4">
+        <v>223.7</v>
+      </c>
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="6" t="s">
@@ -11082,6 +11682,9 @@
       <c r="O40" s="4">
         <v>304.8</v>
       </c>
+      <c r="P40" s="4">
+        <v>328.4999999999999</v>
+      </c>
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="7" t="s">
@@ -11129,6 +11732,9 @@
       <c r="O41" s="4">
         <v>118.7</v>
       </c>
+      <c r="P41" s="4">
+        <v>128.9</v>
+      </c>
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="8" t="s">
@@ -11176,6 +11782,9 @@
       <c r="O42" s="4">
         <v>92.5</v>
       </c>
+      <c r="P42" s="4">
+        <v>99.2</v>
+      </c>
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="9" t="s">
@@ -11223,6 +11832,9 @@
       <c r="O43" s="4">
         <v>344.9999999999999</v>
       </c>
+      <c r="P43" s="4">
+        <v>370.9999999999999</v>
+      </c>
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="10" t="s">
@@ -11270,6 +11882,9 @@
       <c r="O44" s="4">
         <v>295.1</v>
       </c>
+      <c r="P44" s="4">
+        <v>318.1</v>
+      </c>
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="11" t="s">
@@ -11317,6 +11932,9 @@
       <c r="O45" s="4">
         <v>129.6</v>
       </c>
+      <c r="P45" s="4">
+        <v>141.3</v>
+      </c>
     </row>
     <row r="46" spans="1:25">
       <c r="A46" s="12" t="s">
@@ -11364,6 +11982,9 @@
       <c r="O46" s="4">
         <v>400.1999999999999</v>
       </c>
+      <c r="P46" s="4">
+        <v>429.3</v>
+      </c>
     </row>
     <row r="47" spans="1:25">
       <c r="A47" s="13" t="s">
@@ -11411,6 +12032,9 @@
       <c r="O47" s="4">
         <v>88.89999999999998</v>
       </c>
+      <c r="P47" s="4">
+        <v>95.29999999999998</v>
+      </c>
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="1" t="s">
@@ -11530,10 +12154,13 @@
         <v>10.83333333333333</v>
       </c>
       <c r="N50" s="4">
-        <v>9.615384615384615</v>
+        <v>9.23076923076923</v>
       </c>
       <c r="O50" s="4">
-        <v>10.21428571428571</v>
+        <v>9.857142857142858</v>
+      </c>
+      <c r="P50" s="4">
+        <v>10.33333333333333</v>
       </c>
     </row>
     <row r="51" spans="1:25">
@@ -11582,6 +12209,9 @@
       <c r="O51" s="4">
         <v>21.14285714285714</v>
       </c>
+      <c r="P51" s="4">
+        <v>20.86666666666667</v>
+      </c>
     </row>
     <row r="52" spans="1:25">
       <c r="A52" s="6" t="s">
@@ -11629,6 +12259,9 @@
       <c r="O52" s="4">
         <v>55.71428571428572</v>
       </c>
+      <c r="P52" s="4">
+        <v>55.93333333333333</v>
+      </c>
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="7" t="s">
@@ -11676,6 +12309,9 @@
       <c r="O53" s="4">
         <v>14.42857142857143</v>
       </c>
+      <c r="P53" s="4">
+        <v>14.53333333333333</v>
+      </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="8" t="s">
@@ -11723,6 +12359,9 @@
       <c r="O54" s="4">
         <v>5.214285714285714</v>
       </c>
+      <c r="P54" s="4">
+        <v>4.733333333333333</v>
+      </c>
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="9" t="s">
@@ -11770,6 +12409,9 @@
       <c r="O55" s="4">
         <v>54.71428571428572</v>
       </c>
+      <c r="P55" s="4">
+        <v>56.46666666666667</v>
+      </c>
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="10" t="s">
@@ -11817,6 +12459,9 @@
       <c r="O56" s="4">
         <v>44.85714285714285</v>
       </c>
+      <c r="P56" s="4">
+        <v>44.46666666666667</v>
+      </c>
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="11" t="s">
@@ -11862,7 +12507,10 @@
         <v>13.69230769230769</v>
       </c>
       <c r="O57" s="4">
-        <v>13.92857142857143</v>
+        <v>14</v>
+      </c>
+      <c r="P57" s="4">
+        <v>14.06666666666667</v>
       </c>
     </row>
     <row r="58" spans="1:25">
@@ -11906,10 +12554,13 @@
         <v>68.08333333333333</v>
       </c>
       <c r="N58" s="4">
-        <v>66.07692307692308</v>
+        <v>66.46153846153847</v>
       </c>
       <c r="O58" s="4">
-        <v>66.28571428571429</v>
+        <v>66.64285714285714</v>
+      </c>
+      <c r="P58" s="4">
+        <v>65.66666666666667</v>
       </c>
     </row>
     <row r="59" spans="1:25">
@@ -11958,6 +12609,9 @@
       <c r="O59" s="4">
         <v>3.214285714285714</v>
       </c>
+      <c r="P59" s="4">
+        <v>2.866666666666667</v>
+      </c>
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="1" t="s">
@@ -12082,6 +12736,9 @@
       <c r="O62" s="4">
         <v>8.699999999999999</v>
       </c>
+      <c r="P62" s="4">
+        <v>8.799999999999999</v>
+      </c>
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="5" t="s">
@@ -12129,6 +12786,9 @@
       <c r="O63" s="4">
         <v>14.86428571428571</v>
       </c>
+      <c r="P63" s="4">
+        <v>14.91333333333333</v>
+      </c>
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="6" t="s">
@@ -12176,6 +12836,9 @@
       <c r="O64" s="4">
         <v>21.77142857142857</v>
       </c>
+      <c r="P64" s="4">
+        <v>21.9</v>
+      </c>
     </row>
     <row r="65" spans="1:25">
       <c r="A65" s="7" t="s">
@@ -12223,6 +12886,9 @@
       <c r="O65" s="4">
         <v>8.47857142857143</v>
       </c>
+      <c r="P65" s="4">
+        <v>8.593333333333334</v>
+      </c>
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="8" t="s">
@@ -12270,6 +12936,9 @@
       <c r="O66" s="4">
         <v>6.607142857142857</v>
       </c>
+      <c r="P66" s="4">
+        <v>6.613333333333333</v>
+      </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="9" t="s">
@@ -12317,6 +12986,9 @@
       <c r="O67" s="4">
         <v>24.64285714285714</v>
       </c>
+      <c r="P67" s="4">
+        <v>24.73333333333333</v>
+      </c>
     </row>
     <row r="68" spans="1:25">
       <c r="A68" s="10" t="s">
@@ -12364,6 +13036,9 @@
       <c r="O68" s="4">
         <v>21.07857142857143</v>
       </c>
+      <c r="P68" s="4">
+        <v>21.20666666666666</v>
+      </c>
     </row>
     <row r="69" spans="1:25">
       <c r="A69" s="11" t="s">
@@ -12411,6 +13086,9 @@
       <c r="O69" s="4">
         <v>9.257142857142856</v>
       </c>
+      <c r="P69" s="4">
+        <v>9.419999999999998</v>
+      </c>
     </row>
     <row r="70" spans="1:25">
       <c r="A70" s="12" t="s">
@@ -12458,6 +13136,9 @@
       <c r="O70" s="4">
         <v>28.58571428571428</v>
       </c>
+      <c r="P70" s="4">
+        <v>28.62</v>
+      </c>
     </row>
     <row r="71" spans="1:25">
       <c r="A71" s="13" t="s">
@@ -12505,6 +13186,9 @@
       <c r="O71" s="4">
         <v>6.349999999999999</v>
       </c>
+      <c r="P71" s="4">
+        <v>6.353333333333333</v>
+      </c>
     </row>
     <row r="73" spans="1:25">
       <c r="A73" s="1" t="s">
@@ -12624,10 +13308,13 @@
         <v>-1.188118811881188</v>
       </c>
       <c r="N74" s="4">
-        <v>-0.5050505050505051</v>
+        <v>-1.01010101010101</v>
       </c>
       <c r="O74" s="4">
         <v>1.855670103092784</v>
+      </c>
+      <c r="P74" s="4">
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="75" spans="1:25">
@@ -12676,6 +13363,9 @@
       <c r="O75" s="4">
         <v>1.354838709677419</v>
       </c>
+      <c r="P75" s="4">
+        <v>1.08974358974359</v>
+      </c>
     </row>
     <row r="76" spans="1:25">
       <c r="A76" s="6" t="s">
@@ -12723,6 +13413,9 @@
       <c r="O76" s="4">
         <v>2.008547008547009</v>
       </c>
+      <c r="P76" s="4">
+        <v>2.489451476793249</v>
+      </c>
     </row>
     <row r="77" spans="1:25">
       <c r="A77" s="7" t="s">
@@ -12770,6 +13463,9 @@
       <c r="O77" s="4">
         <v>0.6796116504854368</v>
       </c>
+      <c r="P77" s="4">
+        <v>1.568627450980392</v>
+      </c>
     </row>
     <row r="78" spans="1:25">
       <c r="A78" s="8" t="s">
@@ -12817,6 +13513,9 @@
       <c r="O78" s="4">
         <v>-2.028985507246376</v>
       </c>
+      <c r="P78" s="4">
+        <v>-0.2985074626865671</v>
+      </c>
     </row>
     <row r="79" spans="1:25">
       <c r="A79" s="9" t="s">
@@ -12864,6 +13563,9 @@
       <c r="O79" s="4">
         <v>2.586872586872587</v>
       </c>
+      <c r="P79" s="4">
+        <v>3.115384615384615</v>
+      </c>
     </row>
     <row r="80" spans="1:25">
       <c r="A80" s="10" t="s">
@@ -12911,6 +13613,9 @@
       <c r="O80" s="4">
         <v>1.091703056768559</v>
       </c>
+      <c r="P80" s="4">
+        <v>1.695652173913043</v>
+      </c>
     </row>
     <row r="81" spans="1:25">
       <c r="A81" s="11" t="s">
@@ -12956,7 +13661,10 @@
         <v>2.336448598130841</v>
       </c>
       <c r="O81" s="4">
-        <v>1.517857142857143</v>
+        <v>1.607142857142857</v>
+      </c>
+      <c r="P81" s="4">
+        <v>1.282051282051282</v>
       </c>
     </row>
     <row r="82" spans="1:25">
@@ -13000,10 +13708,13 @@
         <v>1.903114186851211</v>
       </c>
       <c r="N82" s="4">
-        <v>1.448275862068966</v>
+        <v>1.620689655172414</v>
       </c>
       <c r="O82" s="4">
         <v>2.379310344827586</v>
+      </c>
+      <c r="P82" s="4">
+        <v>1.786941580756014</v>
       </c>
     </row>
     <row r="83" spans="1:25">
@@ -13052,6 +13763,9 @@
       <c r="O83" s="4">
         <v>0.7692307692307693</v>
       </c>
+      <c r="P83" s="4">
+        <v>-0.3125</v>
+      </c>
     </row>
     <row r="85" spans="1:25">
       <c r="A85" s="1" t="s">
@@ -13171,10 +13885,13 @@
         <v>1.272015655577299</v>
       </c>
       <c r="N86" s="4">
-        <v>1.115075825156111</v>
+        <v>1.070472792149866</v>
       </c>
       <c r="O86" s="4">
-        <v>1.174055829228243</v>
+        <v>1.133004926108374</v>
+      </c>
+      <c r="P86" s="4">
+        <v>1.174242424242424</v>
       </c>
     </row>
     <row r="87" spans="1:25">
@@ -13223,6 +13940,9 @@
       <c r="O87" s="4">
         <v>1.42239308024988</v>
       </c>
+      <c r="P87" s="4">
+        <v>1.399195350916406</v>
+      </c>
     </row>
     <row r="88" spans="1:25">
       <c r="A88" s="6" t="s">
@@ -13270,6 +13990,9 @@
       <c r="O88" s="4">
         <v>2.559055118110236</v>
       </c>
+      <c r="P88" s="4">
+        <v>2.554033485540335</v>
+      </c>
     </row>
     <row r="89" spans="1:25">
       <c r="A89" s="7" t="s">
@@ -13317,6 +14040,9 @@
       <c r="O89" s="4">
         <v>1.701769165964617</v>
       </c>
+      <c r="P89" s="4">
+        <v>1.691233514352211</v>
+      </c>
     </row>
     <row r="90" spans="1:25">
       <c r="A90" s="8" t="s">
@@ -13364,6 +14090,9 @@
       <c r="O90" s="4">
         <v>0.7891891891891892</v>
       </c>
+      <c r="P90" s="4">
+        <v>0.7157258064516129</v>
+      </c>
     </row>
     <row r="91" spans="1:25">
       <c r="A91" s="9" t="s">
@@ -13411,6 +14140,9 @@
       <c r="O91" s="4">
         <v>2.220289855072464</v>
       </c>
+      <c r="P91" s="4">
+        <v>2.283018867924528</v>
+      </c>
     </row>
     <row r="92" spans="1:25">
       <c r="A92" s="10" t="s">
@@ -13458,6 +14190,9 @@
       <c r="O92" s="4">
         <v>2.128092172145035</v>
       </c>
+      <c r="P92" s="4">
+        <v>2.096824897830871</v>
+      </c>
     </row>
     <row r="93" spans="1:25">
       <c r="A93" s="11" t="s">
@@ -13503,7 +14238,10 @@
         <v>1.503378378378378</v>
       </c>
       <c r="O93" s="4">
-        <v>1.50462962962963</v>
+        <v>1.512345679012346</v>
+      </c>
+      <c r="P93" s="4">
+        <v>1.493276716206652</v>
       </c>
     </row>
     <row r="94" spans="1:25">
@@ -13547,10 +14285,13 @@
         <v>2.387492694330801</v>
       </c>
       <c r="N94" s="4">
-        <v>2.314116379310345</v>
+        <v>2.327586206896552</v>
       </c>
       <c r="O94" s="4">
-        <v>2.318840579710145</v>
+        <v>2.331334332833583</v>
+      </c>
+      <c r="P94" s="4">
+        <v>2.294432797577452</v>
       </c>
     </row>
     <row r="95" spans="1:25">
@@ -13598,6 +14339,9 @@
       </c>
       <c r="O95" s="4">
         <v>0.5061867266591675</v>
+      </c>
+      <c r="P95" s="4">
+        <v>0.4512067156348374</v>
       </c>
     </row>
   </sheetData>
